--- a/docs/informes/ree_generacion_2026-09-01.xlsx
+++ b/docs/informes/ree_generacion_2026-09-01.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026 09:43</t>
+          <t>30/09/2026 09:50</t>
         </is>
       </c>
     </row>

--- a/docs/informes/ree_generacion_2026-09-01.xlsx
+++ b/docs/informes/ree_generacion_2026-09-01.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026 09:50</t>
+          <t>30/09/2026 10:07</t>
         </is>
       </c>
     </row>
